--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.73830584314265</v>
+        <v>8.244974699510681</v>
       </c>
       <c r="D2" t="n">
-        <v>50.03053769830025</v>
+        <v>8.129962375973792</v>
       </c>
       <c r="E2" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F2" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.90401871226585</v>
+        <v>7.784403040743201</v>
       </c>
       <c r="D3" t="n">
-        <v>47.40926391878227</v>
+        <v>7.704005386802119</v>
       </c>
       <c r="E3" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F3" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.86974631634092</v>
+        <v>6.3163337764054</v>
       </c>
       <c r="D4" t="n">
-        <v>38.20821686525365</v>
+        <v>6.208835240603718</v>
       </c>
       <c r="E4" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F4" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.16163493350309</v>
+        <v>7.176265676694252</v>
       </c>
       <c r="D5" t="n">
-        <v>44.06876462375524</v>
+        <v>7.161174251360227</v>
       </c>
       <c r="E5" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F5" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.38477631085023</v>
+        <v>2.987526150513163</v>
       </c>
       <c r="D6" t="n">
-        <v>41.11265012134343</v>
+        <v>6.680805644718308</v>
       </c>
       <c r="E6" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F6" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.16552506059644</v>
+        <v>1.976897822346921</v>
       </c>
       <c r="D7" t="n">
-        <v>35.28809997718778</v>
+        <v>5.734316246293014</v>
       </c>
       <c r="E7" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F7" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.73545527679194</v>
+        <v>1.744511482478691</v>
       </c>
       <c r="D8" t="n">
-        <v>32.59601202601324</v>
+        <v>5.296851954227152</v>
       </c>
       <c r="E8" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F8" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.01135777277262</v>
+        <v>1.789345638075551</v>
       </c>
       <c r="D9" t="n">
-        <v>24.9899979991996</v>
+        <v>4.060874674869935</v>
       </c>
       <c r="E9" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F9" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.18033988749895</v>
+        <v>1.816805231718579</v>
       </c>
       <c r="D10" t="n">
-        <v>15.00833101980363</v>
+        <v>2.43885379071809</v>
       </c>
       <c r="E10" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F10" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>50.46347195844811</v>
+        <v>8.200314193247818</v>
       </c>
       <c r="D11" t="n">
-        <v>51.24834474109399</v>
+        <v>8.327856020427774</v>
       </c>
       <c r="E11" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F11" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>70.9242969366351</v>
+        <v>11.5251982522032</v>
       </c>
       <c r="D12" t="n">
-        <v>58.50838456986322</v>
+        <v>9.507612492602775</v>
       </c>
       <c r="E12" t="n">
-        <v>20.31767681701706</v>
+        <v>3.301622482765272</v>
       </c>
       <c r="F12" t="n">
-        <v>11.95555892113893</v>
+        <v>1.942778324685075</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
